--- a/files/camilla_henrik_ugift.xlsx
+++ b/files/camilla_henrik_ugift.xlsx
@@ -1,416 +1,1130 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/thomaspetersen/GIT/sem2.tepedu.dk/files/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_8C59C5722704FF2AACD1988EA7031EF0F94A7625" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="17100" yWindow="700" windowWidth="17100" windowHeight="21440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Parberegning" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Skatteberegner Pro</author>
   </authors>
   <commentList>
-    <comment ref="A6" authorId="0">
-      <text>
-        <t>Din årlige lønindkomst før arbejdsmarkedsbidrag (AM-bidrag på 8%).</t>
-      </text>
-    </comment>
-    <comment ref="A7" authorId="0">
-      <text>
-        <t>Procentdel af lønindkomst der går til arbejdsgiveradministreret pension (eget bidrag). Dette trækkes fra lønindkomsten før AM-bidrag beregnes.</t>
-      </text>
-    </comment>
-    <comment ref="A8" authorId="0">
-      <text>
-        <t>Procentdel af lønindkomst der går til arbejdsgiveradministreret pension (eget bidrag). Dette trækkes fra lønindkomsten før AM-bidrag beregnes.</t>
-      </text>
-    </comment>
-    <comment ref="A9" authorId="0">
-      <text>
-        <t>Arbejdsgiverens indbetaling i procent. Ved 0 bruges standard: 2× eget bidrag. Bruges til beregning af beskæftigelsesfradrag og jobfradrag.</t>
-      </text>
-    </comment>
-    <comment ref="A10" authorId="0">
-      <text>
-        <t>Arbejdsgiverens indbetaling i procent. Ved 0 bruges standard: 2× eget bidrag. Bruges til beregning af beskæftigelsesfradrag og jobfradrag.</t>
-      </text>
-    </comment>
-    <comment ref="A11" authorId="0">
-      <text>
-        <t xml:space="preserve">Privat pensionsindbetaling (livrente eller ratepension). Maksimum 65.500 kr. årligt i alt.
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Din årlige lønindkomst før arbejdsmarkedsbidrag (AM-bidrag på 8%).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Procentdel af lønindkomst der går til arbejdsgiveradministreret pension (eget bidrag). Dette trækkes fra lønindkomsten før AM-bidrag beregnes.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Procentdel af lønindkomst der går til arbejdsgiveradministreret pension (eget bidrag). Dette trækkes fra lønindkomsten før AM-bidrag beregnes.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Arbejdsgiverens indbetaling i procent. Ved 0 bruges standard: 2× eget bidrag. Bruges til beregning af beskæftigelsesfradrag og jobfradrag.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Arbejdsgiverens indbetaling i procent. Ved 0 bruges standard: 2× eget bidrag. Bruges til beregning af beskæftigelsesfradrag og jobfradrag.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Privat pensionsindbetaling (livrente eller ratepension). Maksimum 65.500 kr. årligt i alt.
 Livrente: Udbetales som løbende ydelse resten af livet. Kan ikke hæves som engangsbeløb.
 Ratepension: Udbetales over minimum 10 år. Kan hæves som engangsbeløb (dog med højere beskatning).
 Skattemæssig behandling:
 • Indbetalinger giver skattefradrag (op til 65.500 kr.)
 • Udbetalinger beskattes som kapitalindkomst
 • Begge typer behandles ens skattemæssigt</t>
-      </text>
-    </comment>
-    <comment ref="A12" authorId="0">
-      <text>
-        <t>Anden indkomst der er AM-pligtig (f.eks. honorarer, provisioner).</t>
-      </text>
-    </comment>
-    <comment ref="A13" authorId="0">
-      <text>
-        <t>Hvis du har fri telefon fra arbejdsgiveren, tilføjes 3.300 kr. til din AM-pligtige indkomst.</t>
-      </text>
-    </comment>
-    <comment ref="A14" authorId="0">
-      <text>
-        <t>Hvis du er medlem af folkekirken, betaler du kirkeskat. Kirkesatsen varierer efter kommune.</t>
-      </text>
-    </comment>
-    <comment ref="A15" authorId="0">
-      <text>
-        <t>Din alder bruges til at beregne ekstra pensionsfradrag. Hvis du har under 15 år til pensionsalderen (70 år), får du 32% fradrag i stedet for 12%.</t>
-      </text>
-    </comment>
-    <comment ref="A16" authorId="0">
-      <text>
-        <t>Antal kilometer til og fra arbejde (tur/retur). Fradrag gælder kun for km over 24 km. Høj sats (2,28 kr/km) gælder for 24-120 km, lav sats (1,14 kr/km) for km over 120.</t>
-      </text>
-    </comment>
-    <comment ref="A17" authorId="0">
-      <text>
-        <t>Antal arbejdsdage om året. Standard er 220 dage.</t>
-      </text>
-    </comment>
-    <comment ref="A18" authorId="0">
-      <text>
-        <t>Fagforeningskontingent. Maksimum 7.000 kr. kan fradrages.</t>
-      </text>
-    </comment>
-    <comment ref="A19" authorId="0">
-      <text>
-        <t>Årligt kontingent til A-kasse. Dette kan fradrages som ligningsmæssigt fradrag.</t>
-      </text>
-    </comment>
-    <comment ref="A20" authorId="0">
-      <text>
-        <t>Andre ligningsmæssige fradrag der ikke er dækket af de andre felter.</t>
-      </text>
-    </comment>
-    <comment ref="A21" authorId="0">
-      <text>
-        <t>Årlige renteindtægter (f.eks. fra bankindlån, obligationer). Positiv kapitalindkomst påvirker bundskat og topskat beregning. Hvis positiv kapitalindkomst over 52.400 kr (par: 104.800 kr), påvirker det topskatten med skatteloft på 42%.</t>
-      </text>
-    </comment>
-    <comment ref="A22" authorId="0">
-      <text>
-        <t>Årlige renteudgifter (f.eks. fra lån). Dette trækkes fra renteindtægter for at beregne kapitalindkomst. Negativ kapitalindkomst (renteudgifter større end renteindtægter) giver et skattefradrag, og for negativ kapitalindkomst op til 50.000 kr (enlige) eller 100.000 kr (par) får du en ekstra skatterabat på 8%.</t>
-      </text>
-    </comment>
-    <comment ref="A26" authorId="0">
-      <text>
-        <t>Person 2's årlige lønindkomst før arbejdsmarkedsbidrag (AM-bidrag på 8%).</t>
-      </text>
-    </comment>
-    <comment ref="A27" authorId="0">
-      <text>
-        <t>Procentdel af lønindkomst der går til arbejdsgiveradministreret pension (eget bidrag). Dette trækkes fra lønindkomsten før AM-bidrag beregnes.</t>
-      </text>
-    </comment>
-    <comment ref="A28" authorId="0">
-      <text>
-        <t>Procentdel af lønindkomst der går til arbejdsgiveradministreret pension (eget bidrag). Dette trækkes fra lønindkomsten før AM-bidrag beregnes.</t>
-      </text>
-    </comment>
-    <comment ref="A29" authorId="0">
-      <text>
-        <t>Arbejdsgiverens indbetaling i procent. Ved 0 bruges standard: 2× eget bidrag. Bruges til beregning af beskæftigelsesfradrag og jobfradrag.</t>
-      </text>
-    </comment>
-    <comment ref="A30" authorId="0">
-      <text>
-        <t>Arbejdsgiverens indbetaling i procent. Ved 0 bruges standard: 2× eget bidrag. Bruges til beregning af beskæftigelsesfradrag og jobfradrag.</t>
-      </text>
-    </comment>
-    <comment ref="A31" authorId="0">
-      <text>
-        <t xml:space="preserve">Privat pensionsindbetaling (livrente eller ratepension). Maksimum 65.500 kr. årligt i alt.
+        </r>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Anden indkomst der er AM-pligtig (f.eks. honorarer, provisioner).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Hvis du har fri telefon fra arbejdsgiveren, tilføjes 3.300 kr. til din AM-pligtige indkomst.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Hvis du er medlem af folkekirken, betaler du kirkeskat. Kirkesatsen varierer efter kommune.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Din alder bruges til at beregne ekstra pensionsfradrag. Hvis du har under 15 år til pensionsalderen (70 år), får du 32% fradrag i stedet for 12%.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Antal kilometer til og fra arbejde (tur/retur). Fradrag gælder kun for km over 24 km. Høj sats (2,28 kr/km) gælder for 24-120 km, lav sats (1,14 kr/km) for km over 120.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Antal arbejdsdage om året. Standard er 220 dage.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Fagforeningskontingent. Maksimum 7.000 kr. kan fradrages.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Årligt kontingent til A-kasse. Dette kan fradrages som ligningsmæssigt fradrag.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Andre ligningsmæssige fradrag der ikke er dækket af de andre felter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Årlige renteindtægter (f.eks. fra bankindlån, obligationer). Positiv kapitalindkomst påvirker bundskat og topskat beregning. Hvis positiv kapitalindkomst over 52.400 kr (par: 104.800 kr), påvirker det topskatten med skatteloft på 42%.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Årlige renteudgifter (f.eks. fra lån). Dette trækkes fra renteindtægter for at beregne kapitalindkomst. Negativ kapitalindkomst (renteudgifter større end renteindtægter) giver et skattefradrag, og for negativ kapitalindkomst op til 50.000 kr (enlige) eller 100.000 kr (par) får du en ekstra skatterabat på 8%.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Person 2's årlige lønindkomst før arbejdsmarkedsbidrag (AM-bidrag på 8%).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Procentdel af lønindkomst der går til arbejdsgiveradministreret pension (eget bidrag). Dette trækkes fra lønindkomsten før AM-bidrag beregnes.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Procentdel af lønindkomst der går til arbejdsgiveradministreret pension (eget bidrag). Dette trækkes fra lønindkomsten før AM-bidrag beregnes.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Arbejdsgiverens indbetaling i procent. Ved 0 bruges standard: 2× eget bidrag. Bruges til beregning af beskæftigelsesfradrag og jobfradrag.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Arbejdsgiverens indbetaling i procent. Ved 0 bruges standard: 2× eget bidrag. Bruges til beregning af beskæftigelsesfradrag og jobfradrag.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Privat pensionsindbetaling (livrente eller ratepension). Maksimum 65.500 kr. årligt i alt.
 Livrente: Udbetales som løbende ydelse resten af livet. Kan ikke hæves som engangsbeløb.
 Ratepension: Udbetales over minimum 10 år. Kan hæves som engangsbeløb (dog med højere beskatning).
 Skattemæssig behandling:
 • Indbetalinger giver skattefradrag (op til 65.500 kr.)
 • Udbetalinger beskattes som kapitalindkomst
 • Begge typer behandles ens skattemæssigt</t>
-      </text>
-    </comment>
-    <comment ref="A32" authorId="0">
-      <text>
-        <t>Anden indkomst der er AM-pligtig (f.eks. honorarer, provisioner).</t>
-      </text>
-    </comment>
-    <comment ref="A33" authorId="0">
-      <text>
-        <t>Hvis du har fri telefon fra arbejdsgiveren, tilføjes 3.300 kr. til din AM-pligtige indkomst.</t>
-      </text>
-    </comment>
-    <comment ref="A34" authorId="0">
-      <text>
-        <t>Hvis du er medlem af folkekirken, betaler du kirkeskat. Kirkesatsen varierer efter kommune.</t>
-      </text>
-    </comment>
-    <comment ref="A35" authorId="0">
-      <text>
-        <t>Din alder bruges til at beregne ekstra pensionsfradrag. Hvis du har under 15 år til pensionsalderen (70 år), får du 32% fradrag i stedet for 12%.</t>
-      </text>
-    </comment>
-    <comment ref="A36" authorId="0">
-      <text>
-        <t>Antal kilometer til og fra arbejde (tur/retur). Fradrag gælder kun for km over 24 km. Høj sats (2,28 kr/km) gælder for 24-120 km, lav sats (1,14 kr/km) for km over 120.</t>
-      </text>
-    </comment>
-    <comment ref="A37" authorId="0">
-      <text>
-        <t>Antal arbejdsdage om året. Standard er 220 dage.</t>
-      </text>
-    </comment>
-    <comment ref="A38" authorId="0">
-      <text>
-        <t>Fagforeningskontingent. Maksimum 7.000 kr. kan fradrages.</t>
-      </text>
-    </comment>
-    <comment ref="A39" authorId="0">
-      <text>
-        <t>Årligt kontingent til A-kasse. Dette kan fradrages som ligningsmæssigt fradrag.</t>
-      </text>
-    </comment>
-    <comment ref="A40" authorId="0">
-      <text>
-        <t>Andre ligningsmæssige fradrag der ikke er dækket af de andre felter.</t>
-      </text>
-    </comment>
-    <comment ref="A41" authorId="0">
-      <text>
-        <t>Årlige renteindtægter (f.eks. fra bankindlån, obligationer). Positiv kapitalindkomst påvirker bundskat og topskat beregning. Hvis positiv kapitalindkomst over 52.400 kr (par: 104.800 kr), påvirker det topskatten med skatteloft på 42%.</t>
-      </text>
-    </comment>
-    <comment ref="A42" authorId="0">
-      <text>
-        <t>Årlige renteudgifter (f.eks. fra lån). Dette trækkes fra renteindtægter for at beregne kapitalindkomst. Negativ kapitalindkomst (renteudgifter større end renteindtægter) giver et skattefradrag, og for negativ kapitalindkomst op til 50.000 kr (enlige) eller 100.000 kr (par) får du en ekstra skatterabat på 8%.</t>
-      </text>
-    </comment>
-    <comment ref="A52" authorId="0">
-      <text>
-        <t xml:space="preserve">AM-pligtig indkomst:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Anden indkomst der er AM-pligtig (f.eks. honorarer, provisioner).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Hvis du har fri telefon fra arbejdsgiveren, tilføjes 3.300 kr. til din AM-pligtige indkomst.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Hvis du er medlem af folkekirken, betaler du kirkeskat. Kirkesatsen varierer efter kommune.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Din alder bruges til at beregne ekstra pensionsfradrag. Hvis du har under 15 år til pensionsalderen (70 år), får du 32% fradrag i stedet for 12%.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Antal kilometer til og fra arbejde (tur/retur). Fradrag gælder kun for km over 24 km. Høj sats (2,28 kr/km) gælder for 24-120 km, lav sats (1,14 kr/km) for km over 120.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A37" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Antal arbejdsdage om året. Standard er 220 dage.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A38" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Fagforeningskontingent. Maksimum 7.000 kr. kan fradrages.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A39" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Årligt kontingent til A-kasse. Dette kan fradrages som ligningsmæssigt fradrag.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A40" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Andre ligningsmæssige fradrag der ikke er dækket af de andre felter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A41" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Årlige renteindtægter (f.eks. fra bankindlån, obligationer). Positiv kapitalindkomst påvirker bundskat og topskat beregning. Hvis positiv kapitalindkomst over 52.400 kr (par: 104.800 kr), påvirker det topskatten med skatteloft på 42%.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A42" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Årlige renteudgifter (f.eks. fra lån). Dette trækkes fra renteindtægter for at beregne kapitalindkomst. Negativ kapitalindkomst (renteudgifter større end renteindtægter) giver et skattefradrag, og for negativ kapitalindkomst op til 50.000 kr (enlige) eller 100.000 kr (par) får du en ekstra skatterabat på 8%.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A52" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>AM-pligtig indkomst:
 Person 1: 950.000 kr.
 Person 2: 400.000 kr.
 Total: 1.350.000 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A53" authorId="0">
-      <text>
-        <t xml:space="preserve">AM-bidrag (8%):
+        </r>
+      </text>
+    </comment>
+    <comment ref="A53" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>AM-bidrag (8%):
 Person 1: 950.000 kr. × 8% = 76.000 kr.
 Person 2: 400.000 kr. × 8% = 32.000 kr.
 Total: 108.000 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A54" authorId="0">
-      <text>
-        <t xml:space="preserve">Personlig indkomst:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A54" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Personlig indkomst:
 Person 1: 950.000 kr. − 76.000 kr. = 874.000 kr.
 Person 2: 400.000 kr. − 32.000 kr. = 368.000 kr.
 Total: 1.242.000 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A56" authorId="0">
-      <text>
-        <t>Årlige renteudgifter (f.eks. fra lån). Dette trækkes fra renteindtægter.</t>
-      </text>
-    </comment>
-    <comment ref="A57" authorId="0">
-      <text>
-        <t xml:space="preserve">Kapitalindkomst:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A56" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Årlige renteudgifter (f.eks. fra lån). Dette trækkes fra renteindtægter.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A57" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Kapitalindkomst:
 Person 1: 0 kr. − 80.000 kr. = -80.000 kr.
 Person 2: 0 kr. − 0 kr. = 0 kr.
 Total: -80.000 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A59" authorId="0">
-      <text>
-        <t xml:space="preserve">Befordringsfradrag:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A59" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Befordringsfradrag:
 Person 1: 8.026 kr.
 Person 2: 0 kr.
 Total: 8.026 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A60" authorId="0">
-      <text>
-        <t xml:space="preserve">Fagforening + A-kasse:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A60" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Fagforening + A-kasse:
 Person 1: 13.000 kr.
 Person 2: 13.000 kr.
 Total: 26.000 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A61" authorId="0">
-      <text>
-        <t xml:space="preserve">Beskæftigelsesfradrag (12,75%):
+        </r>
+      </text>
+    </comment>
+    <comment ref="A61" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Beskæftigelsesfradrag (12,75%):
 Person 1: 950.000 kr. × 12,75% = 63.300 kr.
 Person 2: 400.000 kr. × 12,75% = 51.000 kr.
 Total: 114.300 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A62" authorId="0">
-      <text>
-        <t xml:space="preserve">Jobfradrag (4,5%):
+        </r>
+      </text>
+    </comment>
+    <comment ref="A62" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Jobfradrag (4,5%):
 Person 1: 3.100 kr.
 Person 2: 3.100 kr.
 Total: 6.200 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A63" authorId="0">
-      <text>
-        <t xml:space="preserve">Ligningsmæssige fradrag i alt:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A63" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Ligningsmæssige fradrag i alt:
 Person 1: 87.426 kr.
 Person 2: 67.100 kr.
 Total: 154.526 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A65" authorId="0">
-      <text>
-        <t xml:space="preserve">Skattepligtig indkomst:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A65" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Skattepligtig indkomst:
 Person 1: PI (874.000 kr.) + KI (-80.000 kr.) − Fradrag (87.426 kr.) = 706.574 kr.
 Person 2: PI (368.000 kr.) + KI (0 kr.) − Fradrag (67.100 kr.) = 300.900 kr.
 Total: 1.007.474 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A67" authorId="0">
-      <text>
-        <t xml:space="preserve">AM-bidrag (8%):
+        </r>
+      </text>
+    </comment>
+    <comment ref="A67" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>AM-bidrag (8%):
 Person 1: 950.000 kr. × 8% = 76.000 kr.
 Person 2: 400.000 kr. × 8% = 32.000 kr.
 Total: 108.000 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A68" authorId="0">
-      <text>
-        <t xml:space="preserve">Bundskat (12,01%):
+        </r>
+      </text>
+    </comment>
+    <comment ref="A68" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Bundskat (12,01%):
 Person 1: (874.000 kr. − 54.100 kr.) × 12,01% = 98.470 kr.
 Person 2: (368.000 kr. − 54.100 kr.) × 12,01% = 37.699 kr.
 Total: 136.169 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A69" authorId="0">
-      <text>
-        <t xml:space="preserve">Kommuneskat:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A69" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000030000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Kommuneskat:
 Person 1: (706.574 kr. − 54.100 kr.) × 25,6% = 167.033 kr.
 Person 2: (300.900 kr. − 54.100 kr.) × 25,6% = 63.181 kr.
 Total: 230.214 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A70" authorId="0">
-      <text>
-        <t xml:space="preserve">Kirkeskat:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A70" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000031000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Kirkeskat:
 Person 1: (706.574 kr. − 54.100 kr.) × 0,98% = 6.394 kr.
 Person 2: (300.900 kr. − 54.100 kr.) × 0,98% = 2.419 kr.
 Total: 8.813 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A71" authorId="0">
-      <text>
-        <t xml:space="preserve">Mellemskat:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A71" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000032000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Mellemskat:
 Person 1: 16.203 kr.
 Person 2: 0 kr.
 Total: 16.203 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A72" authorId="0">
-      <text>
-        <t xml:space="preserve">Topskat (15%):
+        </r>
+      </text>
+    </comment>
+    <comment ref="A72" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000033000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Topskat (15%):
 Person 1: 7.208 kr.
 Person 2: 0 kr.
 Total: 7.208 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A73" authorId="0">
-      <text>
-        <t xml:space="preserve">Skatterabat neg. KI:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A73" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000034000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Skatterabat neg. KI:
 Person 1: -4.000 kr.
 Person 2: 0 kr.
 Total: -4.000 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A74" authorId="0">
-      <text>
-        <t xml:space="preserve">Skat i alt:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A74" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000035000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Skat i alt:
 Person 1: 367.308 kr.
 Person 2: 135.299 kr.
 Total: 502.607 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A76" authorId="0">
-      <text>
-        <t xml:space="preserve">Brutto indkomst:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A76" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000036000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Brutto indkomst:
 Person 1: 950.000 kr.
 Person 2: 400.000 kr.
 Total: 1.350.000 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A77" authorId="0">
-      <text>
-        <t xml:space="preserve">Skat i alt:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A77" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000037000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Skat i alt:
 Person 1: 367.308 kr.
 Person 2: 135.299 kr.
 Total: 502.607 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A78" authorId="0">
-      <text>
-        <t xml:space="preserve">Netto udbetalt (år):
+        </r>
+      </text>
+    </comment>
+    <comment ref="A78" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000038000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Netto udbetalt (år):
 Person 1: 582.692 kr.
 Person 2: 264.701 kr.
 Total: 847.393 kr.</t>
-      </text>
-    </comment>
-    <comment ref="A79" authorId="0">
-      <text>
-        <t xml:space="preserve">Netto pr. måned:
+        </r>
+      </text>
+    </comment>
+    <comment ref="A79" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000039000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Netto pr. måned:
 Person 1: 48.558 kr.
 Person 2: 22.058 kr.
 Total: 70.616 kr.</t>
+        </r>
       </text>
     </comment>
   </commentList>
 </comments>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
+  <si>
+    <t>SKATTEBEREGNER PRO - PARBEREGNING 2026</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Genereret</t>
+  </si>
+  <si>
+    <t>15.3.2026, 20.52.27</t>
+  </si>
+  <si>
+    <t>PERSON 1 - INPUT</t>
+  </si>
+  <si>
+    <t>Kommune</t>
+  </si>
+  <si>
+    <t>Aalborg</t>
+  </si>
+  <si>
+    <t>Lønindkomst (før AM)</t>
+  </si>
+  <si>
+    <t>% Pension (Eget bidrag %)</t>
+  </si>
+  <si>
+    <t>Pension (Eget bidrag DKK)</t>
+  </si>
+  <si>
+    <t>% Pension (Arbejdsgiver %)</t>
+  </si>
+  <si>
+    <t>Pension (Arbejdsgiver DKK)</t>
+  </si>
+  <si>
+    <t>Privat pension (Livrente/Ratepension)</t>
+  </si>
+  <si>
+    <t>Anden AM-indkomst</t>
+  </si>
+  <si>
+    <t>Fri Telefon</t>
+  </si>
+  <si>
+    <t>Nej</t>
+  </si>
+  <si>
+    <t>Kirke</t>
+  </si>
+  <si>
+    <t>Medlem</t>
+  </si>
+  <si>
+    <t>Alder</t>
+  </si>
+  <si>
+    <t>Km til arbejde (tur/retur)</t>
+  </si>
+  <si>
+    <t>Arbejdsdage pr. år</t>
+  </si>
+  <si>
+    <t>Fagforening</t>
+  </si>
+  <si>
+    <t>A-kasse</t>
+  </si>
+  <si>
+    <t>Andre fradrag</t>
+  </si>
+  <si>
+    <t>Renteindtægter</t>
+  </si>
+  <si>
+    <t>Renteudgifter</t>
+  </si>
+  <si>
+    <t>PERSON 2 - INPUT</t>
+  </si>
+  <si>
+    <t>SAMLET RESULTAT</t>
+  </si>
+  <si>
+    <t>Samlet brutto</t>
+  </si>
+  <si>
+    <t>Samlet skat</t>
+  </si>
+  <si>
+    <t>Samlet udbetalt (år)</t>
+  </si>
+  <si>
+    <t>Samlet udbetalt (md.)</t>
+  </si>
+  <si>
+    <t>DETALJERET BEREGNING</t>
+  </si>
+  <si>
+    <t>PERSON 1</t>
+  </si>
+  <si>
+    <t>PERSON 2</t>
+  </si>
+  <si>
+    <t>SAMLET</t>
+  </si>
+  <si>
+    <t>1. PERSONLIG INDKOMST (PI)</t>
+  </si>
+  <si>
+    <t>AM-pligtig indkomst</t>
+  </si>
+  <si>
+    <t>− AM-bidrag (8%)</t>
+  </si>
+  <si>
+    <t>= Personlig indkomst (PI)</t>
+  </si>
+  <si>
+    <t>2. KAPITALINDKOMST (KI)</t>
+  </si>
+  <si>
+    <t>− Renteudgifter</t>
+  </si>
+  <si>
+    <t>= Kapitalindkomst (KI)</t>
+  </si>
+  <si>
+    <t>3. LIGNINGSMÆSSIGE FRADRAG</t>
+  </si>
+  <si>
+    <t>Befordringsfradrag</t>
+  </si>
+  <si>
+    <t>Fagforening + A-kasse</t>
+  </si>
+  <si>
+    <t>Beskæftigelsesfradrag</t>
+  </si>
+  <si>
+    <t>Jobfradrag</t>
+  </si>
+  <si>
+    <t>= Ligningsmæssige fradrag i alt</t>
+  </si>
+  <si>
+    <t>4. SKATTEPLIGTIG INDKOMST (SI)</t>
+  </si>
+  <si>
+    <t>= Skattepligtig indkomst (SI)</t>
+  </si>
+  <si>
+    <t>5. SKATTEOPGØRELSE</t>
+  </si>
+  <si>
+    <t>AM-bidrag</t>
+  </si>
+  <si>
+    <t>Bundskat (12,01%)</t>
+  </si>
+  <si>
+    <t>Kommuneskat</t>
+  </si>
+  <si>
+    <t>Kirkeskat</t>
+  </si>
+  <si>
+    <t>Mellemskat</t>
+  </si>
+  <si>
+    <t>Topskat</t>
+  </si>
+  <si>
+    <t>Skatterabat neg. KI (8%)</t>
+  </si>
+  <si>
+    <t>Skat i alt</t>
+  </si>
+  <si>
+    <t>6. NETTO UDBETALING</t>
+  </si>
+  <si>
+    <t>Brutto indkomst</t>
+  </si>
+  <si>
+    <t>− Skat i alt</t>
+  </si>
+  <si>
+    <t>= Netto udbetalt (år)</t>
+  </si>
+  <si>
+    <t>= Netto pr. måned</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="60" formatCode="#,##0 &quot;kr.&quot;"/>
-    <numFmt numFmtId="61" formatCode="#,##0.00&quot; %&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="165" formatCode="#,##0\ &quot;kr.&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00&quot; %&quot;"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -440,9 +1154,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="60" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="61" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -450,6 +1164,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -774,468 +1496,467 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D79"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="45.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
+    <col min="2" max="4" width="15.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>SKATTEBEREGNER PRO - PARBEREGNING 2026</v>
-      </c>
-      <c r="B1" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Genereret</v>
-      </c>
-      <c r="B2" t="str">
-        <v>15.3.2026, 20.52.27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v/>
-      </c>
-      <c r="B3" t="str">
-        <v/>
-      </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>PERSON 1 - INPUT</v>
-      </c>
-      <c r="B4" t="str">
-        <v/>
-      </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Kommune</v>
-      </c>
-      <c r="B5" t="str">
-        <v>Aalborg</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Lønindkomst (før AM)</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
       </c>
       <c r="B6" s="1">
         <v>950000</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>% Pension (Eget bidrag %)</v>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Pension (Eget bidrag DKK)</v>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
       </c>
       <c r="B8" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>% Pension (Arbejdsgiver %)</v>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>10</v>
       </c>
       <c r="B9" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Pension (Arbejdsgiver DKK)</v>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>11</v>
       </c>
       <c r="B10" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Privat pension (Livrente/Ratepension)</v>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>12</v>
       </c>
       <c r="B11" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>Anden AM-indkomst</v>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>13</v>
       </c>
       <c r="B12" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>Fri Telefon</v>
-      </c>
-      <c r="B13" t="str">
-        <v>Nej</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>Kirke</v>
-      </c>
-      <c r="B14" t="str">
-        <v>Medlem</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>Alder</v>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>18</v>
       </c>
       <c r="B15" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>Km til arbejde (tur/retur)</v>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>19</v>
       </c>
       <c r="B16" s="3">
         <v>40</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>Arbejdsdage pr. år</v>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>20</v>
       </c>
       <c r="B17" s="3">
         <v>220</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="str">
-        <v>Fagforening</v>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>21</v>
       </c>
       <c r="B18" s="1">
         <v>8000</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="str">
-        <v>A-kasse</v>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>22</v>
       </c>
       <c r="B19" s="1">
         <v>6000</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="str">
-        <v>Andre fradrag</v>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>23</v>
       </c>
       <c r="B20" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="str">
-        <v>Renteindtægter</v>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>24</v>
       </c>
       <c r="B21" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="str">
-        <v>Renteudgifter</v>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>25</v>
       </c>
       <c r="B22" s="1">
         <v>80000</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" t="str">
-        <v/>
-      </c>
-      <c r="B23" t="str">
-        <v/>
-      </c>
-      <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="str">
-        <v>PERSON 2 - INPUT</v>
-      </c>
-      <c r="B24" t="str">
-        <v/>
-      </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="str">
-        <v>Kommune</v>
-      </c>
-      <c r="B25" t="str">
-        <v>Aalborg</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="str">
-        <v>Lønindkomst (før AM)</v>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>7</v>
       </c>
       <c r="B26" s="1">
         <v>400000</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="str">
-        <v>% Pension (Eget bidrag %)</v>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>8</v>
       </c>
       <c r="B27" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="str">
-        <v>Pension (Eget bidrag DKK)</v>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>9</v>
       </c>
       <c r="B28" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>% Pension (Arbejdsgiver %)</v>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>10</v>
       </c>
       <c r="B29" s="2">
         <v>0</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" t="str">
-        <v>Pension (Arbejdsgiver DKK)</v>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>11</v>
       </c>
       <c r="B30" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="str">
-        <v>Privat pension (Livrente/Ratepension)</v>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>12</v>
       </c>
       <c r="B31" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="str">
-        <v>Anden AM-indkomst</v>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>13</v>
       </c>
       <c r="B32" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="str">
-        <v>Fri Telefon</v>
-      </c>
-      <c r="B33" t="str">
-        <v>Nej</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="str">
-        <v>Kirke</v>
-      </c>
-      <c r="B34" t="str">
-        <v>Medlem</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="str">
-        <v>Alder</v>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>14</v>
+      </c>
+      <c r="B33" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>18</v>
       </c>
       <c r="B35" s="3">
         <v>36</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="str">
-        <v>Km til arbejde (tur/retur)</v>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>19</v>
       </c>
       <c r="B36" s="3">
         <v>15</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="str">
-        <v>Arbejdsdage pr. år</v>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>20</v>
       </c>
       <c r="B37" s="3">
         <v>220</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="str">
-        <v>Fagforening</v>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>21</v>
       </c>
       <c r="B38" s="1">
         <v>7000</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="str">
-        <v>A-kasse</v>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>22</v>
       </c>
       <c r="B39" s="1">
         <v>6000</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>Andre fradrag</v>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>23</v>
       </c>
       <c r="B40" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>Renteindtægter</v>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>24</v>
       </c>
       <c r="B41" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>Renteudgifter</v>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>25</v>
       </c>
       <c r="B42" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v/>
-      </c>
-      <c r="B43" t="str">
-        <v/>
-      </c>
-      <c r="C43" t="str">
-        <v/>
-      </c>
-      <c r="D43" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>SAMLET RESULTAT</v>
-      </c>
-      <c r="B44" t="str">
-        <v/>
-      </c>
-      <c r="C44" t="str">
-        <v/>
-      </c>
-      <c r="D44" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="str">
-        <v>Samlet brutto</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="str">
-        <v>Samlet skat</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="str">
-        <v>Samlet udbetalt (år)</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="str">
-        <v>Samlet udbetalt (md.)</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="str">
-        <v/>
-      </c>
-      <c r="B49" t="str">
-        <v/>
-      </c>
-      <c r="C49" t="str">
-        <v/>
-      </c>
-      <c r="D49" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="str">
-        <v>DETALJERET BEREGNING</v>
-      </c>
-      <c r="B50" t="str">
-        <v>PERSON 1</v>
-      </c>
-      <c r="C50" t="str">
-        <v>PERSON 2</v>
-      </c>
-      <c r="D50" t="str">
-        <v>SAMLET</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="str">
-        <v>1. PERSONLIG INDKOMST (PI)</v>
-      </c>
-      <c r="B51" t="str">
-        <v/>
-      </c>
-      <c r="C51" t="str">
-        <v/>
-      </c>
-      <c r="D51" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="str">
-        <v>AM-pligtig indkomst</v>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>1</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>1</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>32</v>
+      </c>
+      <c r="B50" t="s">
+        <v>33</v>
+      </c>
+      <c r="C50" t="s">
+        <v>34</v>
+      </c>
+      <c r="D50" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>37</v>
       </c>
       <c r="B52" s="1">
         <v>950000</v>
@@ -1247,9 +1968,9 @@
         <v>1350000</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="str">
-        <v>− AM-bidrag (8%)</v>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>38</v>
       </c>
       <c r="B53" s="1">
         <v>76000</v>
@@ -1261,9 +1982,9 @@
         <v>108000</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="str">
-        <v>= Personlig indkomst (PI)</v>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>39</v>
       </c>
       <c r="B54" s="1">
         <v>874000</v>
@@ -1275,23 +1996,23 @@
         <v>1242000</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="str">
-        <v>2. KAPITALINDKOMST (KI)</v>
-      </c>
-      <c r="B55" t="str">
-        <v/>
-      </c>
-      <c r="C55" t="str">
-        <v/>
-      </c>
-      <c r="D55" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="str">
-        <v>− Renteudgifter</v>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>40</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>41</v>
       </c>
       <c r="B56" s="1">
         <v>80000</v>
@@ -1303,9 +2024,9 @@
         <v>80000</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="str">
-        <v>= Kapitalindkomst (KI)</v>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>42</v>
       </c>
       <c r="B57" s="1">
         <v>-80000</v>
@@ -1317,23 +2038,23 @@
         <v>-80000</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="str">
-        <v>3. LIGNINGSMÆSSIGE FRADRAG</v>
-      </c>
-      <c r="B58" t="str">
-        <v/>
-      </c>
-      <c r="C58" t="str">
-        <v/>
-      </c>
-      <c r="D58" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="str">
-        <v>Befordringsfradrag</v>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>43</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>44</v>
       </c>
       <c r="B59" s="1">
         <v>8026</v>
@@ -1345,9 +2066,9 @@
         <v>8026</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" t="str">
-        <v>Fagforening + A-kasse</v>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>45</v>
       </c>
       <c r="B60" s="1">
         <v>13000</v>
@@ -1359,9 +2080,9 @@
         <v>26000</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="str">
-        <v>Beskæftigelsesfradrag</v>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>46</v>
       </c>
       <c r="B61" s="1">
         <v>63300</v>
@@ -1373,9 +2094,9 @@
         <v>114300</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" t="str">
-        <v>Jobfradrag</v>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>47</v>
       </c>
       <c r="B62" s="1">
         <v>3100</v>
@@ -1387,9 +2108,9 @@
         <v>6200</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="str">
-        <v>= Ligningsmæssige fradrag i alt</v>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>48</v>
       </c>
       <c r="B63" s="1">
         <v>87426</v>
@@ -1401,23 +2122,23 @@
         <v>154526</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" t="str">
-        <v>4. SKATTEPLIGTIG INDKOMST (SI)</v>
-      </c>
-      <c r="B64" t="str">
-        <v/>
-      </c>
-      <c r="C64" t="str">
-        <v/>
-      </c>
-      <c r="D64" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="str">
-        <v>= Skattepligtig indkomst (SI)</v>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>49</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>50</v>
       </c>
       <c r="B65" s="1">
         <v>706574</v>
@@ -1429,23 +2150,23 @@
         <v>1007474</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="str">
-        <v>5. SKATTEOPGØRELSE</v>
-      </c>
-      <c r="B66" t="str">
-        <v/>
-      </c>
-      <c r="C66" t="str">
-        <v/>
-      </c>
-      <c r="D66" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="str">
-        <v>AM-bidrag</v>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>51</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>52</v>
       </c>
       <c r="B67" s="1">
         <v>76000</v>
@@ -1457,9 +2178,9 @@
         <v>108000</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="str">
-        <v>Bundskat (12,01%)</v>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>53</v>
       </c>
       <c r="B68" s="1">
         <v>98470</v>
@@ -1471,9 +2192,9 @@
         <v>136169</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="str">
-        <v>Kommuneskat</v>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>54</v>
       </c>
       <c r="B69" s="1">
         <v>167033</v>
@@ -1485,9 +2206,9 @@
         <v>230214</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="str">
-        <v>Kirkeskat</v>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>55</v>
       </c>
       <c r="B70" s="1">
         <v>6394</v>
@@ -1499,9 +2220,9 @@
         <v>8813</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="str">
-        <v>Mellemskat</v>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>56</v>
       </c>
       <c r="B71" s="1">
         <v>16203</v>
@@ -1513,9 +2234,9 @@
         <v>16203</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="str">
-        <v>Topskat</v>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>57</v>
       </c>
       <c r="B72" s="1">
         <v>7208</v>
@@ -1527,9 +2248,9 @@
         <v>7208</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="str">
-        <v>Skatterabat neg. KI (8%)</v>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>58</v>
       </c>
       <c r="B73" s="1">
         <v>-4000</v>
@@ -1541,9 +2262,9 @@
         <v>-4000</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" t="str">
-        <v>Skat i alt</v>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>59</v>
       </c>
       <c r="B74" s="1">
         <v>367308</v>
@@ -1555,23 +2276,23 @@
         <v>502607</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="str">
-        <v>6. NETTO UDBETALING</v>
-      </c>
-      <c r="B75" t="str">
-        <v/>
-      </c>
-      <c r="C75" t="str">
-        <v/>
-      </c>
-      <c r="D75" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="str">
-        <v>Brutto indkomst</v>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>60</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>61</v>
       </c>
       <c r="B76" s="1">
         <v>950000</v>
@@ -1583,9 +2304,9 @@
         <v>1350000</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="str">
-        <v>− Skat i alt</v>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>62</v>
       </c>
       <c r="B77" s="1">
         <v>367308</v>
@@ -1597,9 +2318,9 @@
         <v>502607</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="str">
-        <v>= Netto udbetalt (år)</v>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>63</v>
       </c>
       <c r="B78" s="1">
         <v>582692</v>
@@ -1611,9 +2332,9 @@
         <v>847393</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="str">
-        <v>= Netto pr. måned</v>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>64</v>
       </c>
       <c r="B79" s="1">
         <v>48558</v>
@@ -1626,8 +2347,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D79"/>
+    <ignoredError sqref="A1:D79" numberStoredAsText="1"/>
   </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
